--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/post FET_HRM-2031-0280/Panel-28/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/post FET_HRM-2031-0280/Panel-28/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
@@ -434,7 +434,12 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Radius</t>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Space</t>
         </is>
       </c>
     </row>
@@ -446,26 +451,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.06297</v>
+        <v>16.458</v>
       </c>
       <c r="D2" t="n">
-        <v>16.71601</v>
+        <v>16.15707</v>
       </c>
       <c r="E2" t="n">
-        <v>16.69327</v>
+        <v>16.24426</v>
       </c>
       <c r="F2" t="n">
-        <v>42.48518</v>
+        <v>21.83575</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04911</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.83336</v>
+        <v>35.0546</v>
       </c>
     </row>
     <row r="3">
@@ -475,22 +477,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.75975</v>
+        <v>16.86996</v>
       </c>
       <c r="D3" t="n">
-        <v>16.3607</v>
+        <v>15.92612</v>
       </c>
       <c r="E3" t="n">
-        <v>16.58504</v>
+        <v>16.75054</v>
       </c>
       <c r="F3" t="n">
-        <v>42.89032</v>
+        <v>21.31521</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04926</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.79564</v>
+        <v>34.95791</v>
       </c>
     </row>
     <row r="4">
@@ -500,22 +499,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.69417</v>
+        <v>16.76303</v>
       </c>
       <c r="D4" t="n">
-        <v>16.65354</v>
+        <v>16.03249</v>
       </c>
       <c r="E4" t="n">
-        <v>16.53343</v>
+        <v>16.24641</v>
       </c>
       <c r="F4" t="n">
-        <v>41.69021</v>
+        <v>22.31479</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05121</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.89442</v>
+        <v>34.23327</v>
       </c>
     </row>
     <row r="5">
@@ -525,22 +521,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.60223</v>
+        <v>16.52289</v>
       </c>
       <c r="D5" t="n">
-        <v>16.56025</v>
+        <v>16.20948</v>
       </c>
       <c r="E5" t="n">
-        <v>16.90139</v>
+        <v>16.49653</v>
       </c>
       <c r="F5" t="n">
-        <v>43.1033</v>
+        <v>21.72573</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05057</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.82672</v>
+        <v>34.05933</v>
       </c>
     </row>
     <row r="6">
@@ -550,22 +543,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.93444</v>
+        <v>16.87546</v>
       </c>
       <c r="D6" t="n">
-        <v>16.49947</v>
+        <v>15.87384</v>
       </c>
       <c r="E6" t="n">
-        <v>16.5467</v>
+        <v>16.30744</v>
       </c>
       <c r="F6" t="n">
-        <v>43.10962</v>
+        <v>21.61242</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05055</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.83502</v>
+        <v>34.11775</v>
       </c>
     </row>
     <row r="7">
@@ -575,22 +565,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.69557</v>
+        <v>16.95218</v>
       </c>
       <c r="D7" t="n">
-        <v>16.61948</v>
+        <v>15.68669</v>
       </c>
       <c r="E7" t="n">
-        <v>16.7387</v>
+        <v>16.76601</v>
       </c>
       <c r="F7" t="n">
-        <v>42.60395</v>
+        <v>21.66757</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05114</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.80332</v>
+        <v>34.89648</v>
       </c>
     </row>
     <row r="8">
@@ -600,22 +587,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.82056</v>
+        <v>17.36003</v>
       </c>
       <c r="D8" t="n">
-        <v>16.62571</v>
+        <v>16.13342</v>
       </c>
       <c r="E8" t="n">
-        <v>16.52441</v>
+        <v>16.38364</v>
       </c>
       <c r="F8" t="n">
-        <v>42.7982</v>
+        <v>21.69627</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05154</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.80603</v>
+        <v>33.99167</v>
       </c>
     </row>
     <row r="9">
@@ -625,22 +609,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.60905</v>
+        <v>16.6595</v>
       </c>
       <c r="D9" t="n">
-        <v>16.70618</v>
+        <v>16.21931</v>
       </c>
       <c r="E9" t="n">
-        <v>16.6229</v>
+        <v>16.29833</v>
       </c>
       <c r="F9" t="n">
-        <v>42.49769</v>
+        <v>21.78223</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0509</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.82437</v>
+        <v>34.39618</v>
       </c>
     </row>
     <row r="10">
@@ -650,31 +631,48 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.65386</v>
+        <v>16.69483</v>
       </c>
       <c r="D10" t="n">
-        <v>16.66634</v>
+        <v>15.81473</v>
       </c>
       <c r="E10" t="n">
-        <v>16.83568</v>
+        <v>16.58323</v>
       </c>
       <c r="F10" t="n">
-        <v>42.54352</v>
+        <v>21.54236</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05164</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.81925</v>
+        <v>34.24757</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>Dimple</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -688,14 +686,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>via 1</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.61902</v>
+        <v>17.16129</v>
       </c>
       <c r="D12" t="n">
-        <v>1.10085</v>
+        <v>16.68324</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.88339</v>
+      </c>
+      <c r="F12" t="n">
+        <v>42.49344</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.04987</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.8383</v>
       </c>
     </row>
     <row r="13">
@@ -705,10 +715,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.6155</v>
+        <v>16.9427</v>
       </c>
       <c r="D13" t="n">
-        <v>1.10711</v>
+        <v>16.6363</v>
+      </c>
+      <c r="E13" t="n">
+        <v>16.68648</v>
+      </c>
+      <c r="F13" t="n">
+        <v>43.28182</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.04922</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.84435</v>
       </c>
     </row>
     <row r="14">
@@ -718,10 +740,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.60189</v>
+        <v>16.8002</v>
       </c>
       <c r="D14" t="n">
-        <v>1.10882</v>
+        <v>16.37313</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16.61533</v>
+      </c>
+      <c r="F14" t="n">
+        <v>42.23868</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.05078</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.80732</v>
       </c>
     </row>
     <row r="15">
@@ -731,10 +765,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.59478</v>
+        <v>16.86727</v>
       </c>
       <c r="D15" t="n">
-        <v>1.11343</v>
+        <v>16.61615</v>
+      </c>
+      <c r="E15" t="n">
+        <v>16.79917</v>
+      </c>
+      <c r="F15" t="n">
+        <v>42.64552</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.04972</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.82874</v>
       </c>
     </row>
     <row r="16">
@@ -744,10 +790,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.60434</v>
+        <v>16.61497</v>
       </c>
       <c r="D16" t="n">
-        <v>1.13035</v>
+        <v>16.34659</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16.48556</v>
+      </c>
+      <c r="F16" t="n">
+        <v>42.2466</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.05106</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.84131</v>
       </c>
     </row>
     <row r="17">
@@ -757,10 +815,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.61103</v>
+        <v>16.92031</v>
       </c>
       <c r="D17" t="n">
-        <v>1.12204</v>
+        <v>16.47368</v>
+      </c>
+      <c r="E17" t="n">
+        <v>16.49636</v>
+      </c>
+      <c r="F17" t="n">
+        <v>42.92627</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.05148</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.83989</v>
       </c>
     </row>
     <row r="18">
@@ -770,10 +840,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.61814</v>
+        <v>17.04602</v>
       </c>
       <c r="D18" t="n">
-        <v>1.10661</v>
+        <v>16.66667</v>
+      </c>
+      <c r="E18" t="n">
+        <v>16.95215</v>
+      </c>
+      <c r="F18" t="n">
+        <v>42.13069</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.05038</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.80874</v>
       </c>
     </row>
     <row r="19">
@@ -783,10 +865,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.60276</v>
+        <v>16.93169</v>
       </c>
       <c r="D19" t="n">
-        <v>1.11115</v>
+        <v>16.54577</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.56587</v>
+      </c>
+      <c r="F19" t="n">
+        <v>41.99435</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.05098</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.82471</v>
       </c>
     </row>
     <row r="20">
@@ -796,10 +890,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.6052999999999999</v>
+        <v>16.87902</v>
       </c>
       <c r="D20" t="n">
-        <v>1.11465</v>
+        <v>16.37434</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16.70375</v>
+      </c>
+      <c r="F20" t="n">
+        <v>41.21902</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.05159</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.79036</v>
       </c>
     </row>
   </sheetData>
